--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486740_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486740_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1081</v>
+        <v>3.3549</v>
       </c>
       <c r="E2" t="n">
-        <v>6.759</v>
+        <v>6.5521</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.6509</v>
+        <v>-3.1972</v>
       </c>
       <c r="G2" t="n">
         <v>2.1232</v>
@@ -610,13 +610,13 @@
         <v>0.9654</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0428</v>
+        <v>0.2896</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1098</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.3867</v>
       </c>
       <c r="V2" t="n">
         <v>0.9421</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4679</v>
+        <v>1.9231</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6405</v>
+        <v>4.8474</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.1726</v>
+        <v>-2.9243</v>
       </c>
       <c r="G3" t="n">
         <v>2.6033</v>
@@ -688,13 +688,13 @@
         <v>0.9654</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1933</v>
+        <v>0.2618</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.2063</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1927</v>
+        <v>0.0556</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9421</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7076</v>
+        <v>0.4303</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7282</v>
+        <v>3.6248</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.0207</v>
+        <v>-3.1945</v>
       </c>
       <c r="G4" t="n">
         <v>0.9273</v>
@@ -766,13 +766,13 @@
         <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4634</v>
+        <v>0.1861</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1098</v>
+        <v>0.0063</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3536</v>
+        <v>0.1798</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8415</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CABRERA CABRERA</t>
+          <t>A. CHACON GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3544</v>
+        <v>0.2598</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3822</v>
+        <v>0.9696</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0278</v>
+        <v>-0.7098</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2</v>
+        <v>-0.4445</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7999000000000001</v>
+        <v>1.1583</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4002</v>
+        <v>-1.6028</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.317</v>
+        <v>0.6321</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.317</v>
+        <v>1.1588</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.883</v>
+        <v>-1.0766</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4829</v>
+        <v>-0.0005</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4002</v>
+        <v>-1.0761</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0758</v>
+        <v>0.6963</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4136</v>
+        <v>0.3376</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6622</v>
+        <v>0.3587</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2856</v>
+        <v>-0.5712</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1353</v>
+        <v>-0.007</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.0344</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0663</v>
+        <v>-0.0415</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2346</v>
@@ -922,13 +922,13 @@
         <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.0344</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CHACON GARCIA</t>
+          <t>D. CABRERA CABRERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1498</v>
+        <v>-0.3076</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6593</v>
+        <v>-0.0315</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8091</v>
+        <v>-0.2761</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4445</v>
+        <v>-1.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1583</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6028</v>
+        <v>-0.4002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6321</v>
+        <v>-0.317</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1588</v>
+        <v>-0.317</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0766</v>
+        <v>-0.883</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0005</v>
+        <v>-0.4829</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0761</v>
+        <v>-0.4002</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2867</v>
+        <v>0.4137</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0273</v>
+        <v>-0.0001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2594</v>
+        <v>0.4139</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5712</v>
+        <v>0.2856</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6132</v>
+        <v>-0.5387</v>
       </c>
       <c r="E8" t="n">
         <v>0.3858</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9989</v>
+        <v>-0.9245</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0008</v>
@@ -1078,13 +1078,13 @@
         <v>0.3862</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2262</v>
+        <v>-0.1518</v>
       </c>
       <c r="T8" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V8" t="n">
         <v>1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7938</v>
+        <v>-1.133</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.2924</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4999</v>
+        <v>-1.4254</v>
       </c>
       <c r="G9" t="n">
         <v>0.237</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4632</v>
+        <v>0.124</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4136</v>
+        <v>-0.0001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5286</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4896</v>
+        <v>-2.0841</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1931</v>
+        <v>0.0137</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2965</v>
+        <v>-2.0978</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6522</v>
@@ -1234,13 +1234,13 @@
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1047</v>
+        <v>0.5102</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3305</v>
+        <v>0.5373</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2258</v>
+        <v>-0.0272</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9421</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.171</v>
+        <v>-2.811</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4312</v>
+        <v>-2.121</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7397</v>
+        <v>-0.6901</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6897</v>
@@ -1312,13 +1312,13 @@
         <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1876</v>
+        <v>0.1723</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4966</v>
+        <v>-0.1864</v>
       </c>
       <c r="U11" t="n">
-        <v>0.309</v>
+        <v>0.3587</v>
       </c>
       <c r="V11" t="n">
         <v>0.2856</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8242</v>
+        <v>-4.6256</v>
       </c>
       <c r="E12" t="n">
         <v>-2.3735</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4507</v>
+        <v>-2.2521</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7704</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6676</v>
+        <v>-0.469</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2486</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.419</v>
+        <v>-0.2204</v>
       </c>
       <c r="V12" t="n">
         <v>0.6138</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.538899999999999</v>
+        <v>-5.5389</v>
       </c>
       <c r="E13" t="n">
-        <v>12.1943</v>
+        <v>12.1942</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.7331</v>
+        <v>-17.7333</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.101400000000001</v>
+        <v>-7.1014</v>
       </c>
       <c r="H13" t="n">
         <v>3.7948</v>
@@ -1444,7 +1444,7 @@
         <v>10.8044</v>
       </c>
       <c r="K13" t="n">
-        <v>9.6622</v>
+        <v>9.662200000000002</v>
       </c>
       <c r="L13" t="n">
         <v>1.1422</v>
@@ -1468,13 +1468,13 @@
         <v>6.757899999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>2.068099999999999</v>
+        <v>2.0676</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2725000000000001</v>
+        <v>0.2724</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7957</v>
+        <v>1.7956</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4707</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3219</v>
+        <v>5.6736</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7027</v>
+        <v>6.8061</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3808</v>
+        <v>-1.1325</v>
       </c>
       <c r="G14" t="n">
         <v>1.153</v>
@@ -1546,13 +1546,13 @@
         <v>0.9654</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9929</v>
+        <v>-0.6412</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3314</v>
+        <v>-0.228</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6615</v>
+        <v>-0.4132</v>
       </c>
       <c r="V14" t="n">
         <v>4.5825</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.316</v>
+        <v>4.134</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1486</v>
+        <v>4.9418</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8326</v>
+        <v>-0.8078</v>
       </c>
       <c r="G15" t="n">
         <v>2.4978</v>
@@ -1624,13 +1624,13 @@
         <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2317</v>
+        <v>-0.4137</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2486</v>
+        <v>-0.4555</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0169</v>
+        <v>0.0417</v>
       </c>
       <c r="V15" t="n">
         <v>1.4707</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8957</v>
+        <v>1.7093</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4583</v>
+        <v>4.7685</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5626</v>
+        <v>-3.0592</v>
       </c>
       <c r="G16" t="n">
         <v>2.872</v>
@@ -1702,13 +1702,13 @@
         <v>0.9654</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0004</v>
+        <v>-0.186</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6347</v>
+        <v>-0.3244</v>
       </c>
       <c r="U16" t="n">
-        <v>0.635</v>
+        <v>0.1384</v>
       </c>
       <c r="V16" t="n">
         <v>-1.5559</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3247</v>
+        <v>0.7591</v>
       </c>
       <c r="E17" t="n">
-        <v>2.115</v>
+        <v>2.4252</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7902</v>
+        <v>-1.6661</v>
       </c>
       <c r="G17" t="n">
         <v>2.4209</v>
@@ -1780,13 +1780,13 @@
         <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3238</v>
+        <v>-0.8894</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9933</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3306</v>
+        <v>-0.2064</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2516</v>
+        <v>0.2268</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0145</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2661</v>
+        <v>0.2413</v>
       </c>
       <c r="G18" t="n">
         <v>0.0475</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2042</v>
+        <v>0.1793</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2594</v>
+        <v>0.2345</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>J. VALDERREY PULIDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3769</v>
+        <v>0.0664</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1582</v>
+        <v>-0.6219</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2187</v>
+        <v>0.6884</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4396</v>
+        <v>0.3007</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0275</v>
+        <v>-1.1733</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4671</v>
+        <v>1.474</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7096</v>
+        <v>0.137</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6282</v>
+        <v>-0.4826</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0814</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.27</v>
+        <v>0.1637</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6557</v>
+        <v>-0.6907</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3857</v>
+        <v>0.8544</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3169</v>
+        <v>-0.5792</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7708</v>
+        <v>-0.4273</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8201</v>
+        <v>-0.1797</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0493</v>
+        <v>-0.2477</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. VALDERREY PULIDO</t>
+          <t>A. ROSALES DARIAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6534</v>
+        <v>-1.1075</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2425</v>
+        <v>-0.9801</v>
       </c>
       <c r="F20" t="n">
-        <v>0.589</v>
+        <v>-0.1274</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3007</v>
+        <v>-2.4565</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1733</v>
+        <v>-1.9931</v>
       </c>
       <c r="I20" t="n">
-        <v>1.474</v>
+        <v>-0.4634</v>
       </c>
       <c r="J20" t="n">
-        <v>0.137</v>
+        <v>-1.8422</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4826</v>
+        <v>-1.2341</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6195000000000001</v>
+        <v>-0.6081</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1637</v>
+        <v>-0.6143</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6907</v>
+        <v>-0.759</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8544</v>
+        <v>0.1447</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1472</v>
+        <v>0.0208</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8002</v>
+        <v>-0.1725</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.347</v>
+        <v>0.1933</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ROSALES DARIAS</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1613</v>
+        <v>-1.3708</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0835</v>
+        <v>2.6913</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-4.062</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4565</v>
+        <v>1.1728</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9931</v>
+        <v>-1.2009</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4634</v>
+        <v>2.3738</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8422</v>
+        <v>3.9604</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2341</v>
+        <v>0.2483</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6081</v>
+        <v>3.7121</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6143</v>
+        <v>-2.7876</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.759</v>
+        <v>-1.4492</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1447</v>
+        <v>-1.3384</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3862</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R21" t="n">
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.033</v>
+        <v>-0.1655</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2759</v>
+        <v>-0.1107</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2429</v>
+        <v>-0.0548</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9421</v>
+        <v>-1.7989</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2856</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4204</v>
+        <v>-1.6924</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6913</v>
+        <v>-1.3992</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.1117</v>
+        <v>-0.2932</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1728</v>
+        <v>0.4396</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2009</v>
+        <v>-1.0275</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3738</v>
+        <v>1.4671</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9604</v>
+        <v>0.7096</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2483</v>
+        <v>0.6282</v>
       </c>
       <c r="L22" t="n">
-        <v>3.7121</v>
+        <v>0.0814</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7876</v>
+        <v>-0.27</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4492</v>
+        <v>-1.6557</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3384</v>
+        <v>1.3857</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5792</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1585</v>
+        <v>-2.3169</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2152</v>
+        <v>0.4552</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1107</v>
+        <v>0.579</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1044</v>
+        <v>-0.1238</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7989</v>
+        <v>-0.6565</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7989</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9589</v>
+        <v>-2.8595</v>
       </c>
       <c r="E23" t="n">
         <v>-0.884</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0749</v>
+        <v>-1.9756</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3462</v>
@@ -2248,13 +2248,13 @@
         <v>0.1931</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0993</v>
+        <v>-0</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.1655</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5133</v>
@@ -2287,10 +2287,10 @@
         <v>17.7332</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.1942</v>
+        <v>-12.1941</v>
       </c>
       <c r="G24" t="n">
-        <v>7.101599999999999</v>
+        <v>7.101600000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-3.7948</v>
@@ -2302,7 +2302,7 @@
         <v>17.9058</v>
       </c>
       <c r="K24" t="n">
-        <v>5.867100000000001</v>
+        <v>5.8671</v>
       </c>
       <c r="L24" t="n">
         <v>12.0384</v>
@@ -2323,25 +2323,25 @@
         <v>-6.7578</v>
       </c>
       <c r="R24" t="n">
-        <v>5.792300000000001</v>
+        <v>5.7923</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0677</v>
+        <v>-2.0678</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.7954</v>
+        <v>-1.7955</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2723999999999999</v>
+        <v>-0.2725000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4707</v>
+        <v>1.470699999999999</v>
       </c>
       <c r="W24" t="n">
         <v>8.380699999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.9099</v>
+        <v>-6.909899999999999</v>
       </c>
     </row>
   </sheetData>
